--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99306</v>
+        <v>99307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99307</v>
+        <v>99320</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99320</v>
+        <v>99321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99321</v>
+        <v>99324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx
@@ -6251,7 +6251,7 @@
         <v>136011680</v>
       </c>
       <c r="B50" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
